--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487198_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487198_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6713</v>
+        <v>6.5549</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5679</v>
+        <v>4.8262</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1034</v>
+        <v>1.7287</v>
       </c>
       <c r="G2" t="n">
         <v>4.4514</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>1.548</v>
+        <v>0.4316</v>
       </c>
       <c r="T2" t="n">
-        <v>0.739</v>
+        <v>-0.0026</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.4342</v>
       </c>
       <c r="V2" t="n">
         <v>0.8999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9266</v>
+        <v>3.4506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4052</v>
+        <v>2.4765</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5214</v>
+        <v>0.9742</v>
       </c>
       <c r="G3" t="n">
-        <v>0.405</v>
+        <v>-2.2128</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8498</v>
+        <v>-1.0711</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4448</v>
+        <v>-1.1417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7252</v>
+        <v>-0.5177</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0854</v>
+        <v>0.8589</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3602</v>
+        <v>-1.3766</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3202</v>
+        <v>-1.6951</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2356</v>
+        <v>-1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9154</v>
+        <v>0.2349</v>
       </c>
       <c r="P3" t="n">
-        <v>0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3161</v>
+        <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9076</v>
+        <v>-0.6464</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3821</v>
+        <v>-0.4712</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5255</v>
+        <v>-0.1752</v>
       </c>
       <c r="V3" t="n">
-        <v>1.228</v>
+        <v>7.0819</v>
       </c>
       <c r="W3" t="n">
-        <v>1.228</v>
+        <v>7.3256</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2771</v>
+        <v>2.7765</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5025</v>
+        <v>0.0046</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7747000000000001</v>
+        <v>2.7718</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5311</v>
+        <v>0.405</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4667</v>
+        <v>0.8498</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9978</v>
+        <v>-0.4448</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0117</v>
+        <v>0.7252</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3314</v>
+        <v>2.0854</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3431</v>
+        <v>-1.3602</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4805</v>
+        <v>-0.3202</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1353</v>
+        <v>-1.2356</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.9154</v>
       </c>
       <c r="P4" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.158</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6881</v>
+        <v>0.7575</v>
       </c>
       <c r="T4" t="n">
-        <v>0.591</v>
+        <v>-0.0185</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8999</v>
+        <v>1.228</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8999</v>
+        <v>1.228</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2014</v>
+        <v>2.596</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8161</v>
+        <v>1.9016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3852</v>
+        <v>0.6944</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2128</v>
+        <v>0.5311</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0711</v>
+        <v>-1.4667</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1417</v>
+        <v>1.9978</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5177</v>
+        <v>1.0117</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8589</v>
+        <v>-0.3314</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3766</v>
+        <v>1.3431</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6951</v>
+        <v>-0.4805</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.93</v>
+        <v>-1.1353</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2349</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0881</v>
+        <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8957</v>
+        <v>0.0069</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1316</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7641</v>
+        <v>0.0168</v>
       </c>
       <c r="V5" t="n">
-        <v>7.0819</v>
+        <v>0.8999</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3256</v>
+        <v>0.8999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1868</v>
+        <v>0.4941</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6188</v>
+        <v>-0.4185</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8056</v>
+        <v>0.9127</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2706</v>
@@ -922,13 +922,13 @@
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7006</v>
+        <v>-0.3933</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4614</v>
+        <v>-0.2611</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2393</v>
+        <v>-0.1322</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3461</v>
+        <v>-0.2391</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9236</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5775</v>
+        <v>0.6846</v>
       </c>
       <c r="G7" t="n">
         <v>0.295</v>
@@ -1000,13 +1000,13 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.7271</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5367</v>
+        <v>-0.4297</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>G. AZANZA TERUEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.6583</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.163</v>
+        <v>-0.0964</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.524</v>
+        <v>-0.5619</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8119</v>
+        <v>0.4692</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1315</v>
+        <v>-0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6805</v>
+        <v>0.5748</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0155</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0155</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8274</v>
+        <v>0.3871</v>
       </c>
       <c r="N8" t="n">
         <v>-0.1469</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6805</v>
+        <v>0.5341</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.3857</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1104</v>
+        <v>-0.2072</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. AZANZA TERUEL</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7386</v>
+        <v>-0.7078</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0964</v>
+        <v>-0.1035</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6422</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4692</v>
+        <v>-0.8119</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1055</v>
+        <v>-0.1315</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5748</v>
+        <v>-0.6805</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0155</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0414</v>
+        <v>0.0155</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3871</v>
+        <v>-0.8274</v>
       </c>
       <c r="N9" t="n">
         <v>-0.1469</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5341</v>
+        <v>-0.6805</v>
       </c>
       <c r="P9" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.466</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1785</v>
+        <v>-0.119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2875</v>
+        <v>0.0301</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2521</v>
+        <v>-0.912</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1769</v>
+        <v>0.0829</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0752</v>
+        <v>-0.9949</v>
       </c>
       <c r="G10" t="n">
         <v>-0.024</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.228</v>
+        <v>0.112</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5354</v>
+        <v>-0.2756</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3073</v>
+        <v>0.3876</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9962</v>
+        <v>-3.2685</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.193</v>
+        <v>-2.733</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8032</v>
+        <v>-0.5355</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9340000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6835</v>
+        <v>0.0443</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4772</v>
+        <v>-0.0172</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2062</v>
+        <v>0.0614</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7997</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8526</v>
+        <v>-5.3985</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4198</v>
+        <v>-2.0192</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4329</v>
+        <v>-3.3793</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2335</v>
@@ -1390,13 +1390,13 @@
         <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9003</v>
+        <v>-0.4462</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9967</v>
+        <v>-0.5962</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0965</v>
+        <v>0.15</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6839</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.390599999999998</v>
+        <v>4.687899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.700199999999999</v>
+        <v>2.9976</v>
       </c>
       <c r="F13" t="n">
-        <v>1.690300000000001</v>
+        <v>1.690499999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3351000000000002</v>
@@ -1438,13 +1438,13 @@
         <v>-0.3672999999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03220000000000019</v>
+        <v>0.03219999999999997</v>
       </c>
       <c r="J13" t="n">
         <v>3.4673</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2802</v>
+        <v>7.280200000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-3.812600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.4055</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6327</v>
+        <v>-1.3353</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.5446</v>
+        <v>-2.2472</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9120000000000001</v>
+        <v>0.9117999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.4983</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8132</v>
+        <v>4.2531</v>
       </c>
       <c r="E14" t="n">
-        <v>3.326</v>
+        <v>3.5263</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4872</v>
+        <v>0.7268</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0068</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0429</v>
+        <v>0.4828</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5671</v>
+        <v>-0.3668</v>
       </c>
       <c r="U14" t="n">
-        <v>0.61</v>
+        <v>0.8497</v>
       </c>
       <c r="V14" t="n">
         <v>2.619</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8943</v>
+        <v>2.8227</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0165</v>
+        <v>1.5172</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8778</v>
+        <v>1.3054</v>
       </c>
       <c r="G15" t="n">
         <v>4.8604</v>
@@ -1624,13 +1624,13 @@
         <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8129999999999999</v>
+        <v>0.1153</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9373</v>
+        <v>-0.4366</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1242</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.1631</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7747</v>
+        <v>2.4297</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4294</v>
+        <v>1.2291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3453</v>
+        <v>1.2006</v>
       </c>
       <c r="G16" t="n">
         <v>1.3786</v>
@@ -1702,13 +1702,13 @@
         <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0053</v>
+        <v>0.6603</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3385</v>
+        <v>0.1382</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3332</v>
+        <v>0.5221</v>
       </c>
       <c r="V16" t="n">
         <v>2.1278</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.924</v>
+        <v>1.5919</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8981</v>
+        <v>2.2986</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9741</v>
+        <v>-0.7068</v>
       </c>
       <c r="G17" t="n">
         <v>1.8773</v>
@@ -1780,13 +1780,13 @@
         <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.1048</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6253</v>
+        <v>-0.2247</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1474</v>
+        <v>0.12</v>
       </c>
       <c r="V17" t="n">
         <v>0.2053</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>A. AZKOAGA BENDEJACQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1418</v>
+        <v>0.2045</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3245</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1826</v>
+        <v>0.2828</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5913</v>
+        <v>0.1936</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1664</v>
+        <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4248</v>
+        <v>0.1335</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4513</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2381</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2131</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.14</v>
+        <v>0.1936</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9283</v>
+        <v>0.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7883</v>
+        <v>0.1335</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.386</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5857</v>
+        <v>0.0109</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6359</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9498</v>
+        <v>0.0892</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5334</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0699</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. AZKOAGA BENDEJACQ</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0508</v>
+        <v>-0.4048</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1785</v>
+        <v>0.1674</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2293</v>
+        <v>-0.5722</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1936</v>
+        <v>0.3519</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06</v>
+        <v>0.7524</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1335</v>
+        <v>-0.4006</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.3053</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.9729</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.6676</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1936</v>
+        <v>0.0466</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06</v>
+        <v>-0.2204</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1335</v>
+        <v>0.267</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1428</v>
+        <v>0.0853</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1785</v>
+        <v>-0.1378</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0357</v>
+        <v>0.2231</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6388</v>
+        <v>-0.6199</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0673</v>
+        <v>-0.2764</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.3436</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3519</v>
+        <v>-1.5913</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7524</v>
+        <v>-1.1664</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4006</v>
+        <v>-0.4248</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3053</v>
+        <v>-1.4513</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9729</v>
+        <v>-0.2381</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6676</v>
+        <v>-1.2131</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0466</v>
+        <v>-0.14</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2204</v>
+        <v>-0.9283</v>
       </c>
       <c r="O21" t="n">
-        <v>0.267</v>
+        <v>0.7883</v>
       </c>
       <c r="P21" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1487</v>
+        <v>0.8239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.238</v>
+        <v>0.0351</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0892</v>
+        <v>0.7889</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.228</v>
+        <v>0.5334</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.0699</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.228</v>
+        <v>-2.5365</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7686</v>
+        <v>-1.7888</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7967</v>
+        <v>-2.8968</v>
       </c>
       <c r="F22" t="n">
-        <v>1.028</v>
+        <v>1.108</v>
       </c>
       <c r="G22" t="n">
         <v>-1.881</v>
@@ -2170,13 +2170,13 @@
         <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4984</v>
+        <v>0.4782</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0912</v>
+        <v>-0.1913</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5896</v>
+        <v>0.6696</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5647</v>
+        <v>-2.4371</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8063</v>
+        <v>-1.5073</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7584</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9081</v>
@@ -2248,13 +2248,13 @@
         <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7291</v>
+        <v>0.8566</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9466</v>
+        <v>0.2456</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2175</v>
+        <v>0.6111</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5787</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.150700000000001</v>
+        <v>-7.9048</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2566</v>
+        <v>-5.9561</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8942</v>
+        <v>-1.9487</v>
       </c>
       <c r="G24" t="n">
         <v>-4.073</v>
@@ -2326,13 +2326,13 @@
         <v>0.965</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6484</v>
+        <v>0.8943</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1956</v>
+        <v>0.1048</v>
       </c>
       <c r="U24" t="n">
-        <v>0.844</v>
+        <v>0.7895</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3401</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3905</v>
+        <v>-1.72</v>
       </c>
       <c r="E25" t="n">
         <v>-1.976299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4143</v>
+        <v>0.2558999999999996</v>
       </c>
       <c r="G25" t="n">
         <v>0.3350999999999997</v>
@@ -2389,10 +2389,10 @@
         <v>-3.467300000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.2802</v>
+        <v>-7.280200000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8125</v>
+        <v>3.812499999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-3.8602</v>
@@ -2404,13 +2404,13 @@
         <v>12.5456</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6326</v>
+        <v>4.3028</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9119999999999998</v>
+        <v>-0.9117999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5444</v>
+        <v>5.2151</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4982</v>
